--- a/output/pdf_financials_xlsx/VENI.xlsx
+++ b/output/pdf_financials_xlsx/VENI.xlsx
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>1.435062</v>
+        <v>4.890031</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.435062</v>
+        <v>4.890031</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.890031</v>
+        <v>4.931476</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>4.890031</v>
+        <v>4.931476</v>
       </c>
     </row>
     <row r="93">
@@ -4006,7 +4006,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>3.454969</v>
       </c>

--- a/output/pdf_financials_xlsx/VENI.xlsx
+++ b/output/pdf_financials_xlsx/VENI.xlsx
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.372402</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.396744</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.029528</v>
       </c>
     </row>
     <row r="13">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.77682</v>
+        <v>-1.149222</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.696246</v>
+        <v>-1.09299</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.533571</v>
+        <v>-4.563099</v>
       </c>
     </row>
     <row r="28">
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.77611</v>
+        <v>-1.148512</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.603799</v>
+        <v>-1.000543</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.857989</v>
+        <v>-3.887517</v>
       </c>
     </row>
     <row r="30">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-96.1361768591738</v>
+        <v>-96.87197704686166</v>
       </c>
     </row>
     <row r="31">
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07277699999999999</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.560507</v>
       </c>
     </row>
     <row r="125">
@@ -2922,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07277699999999999</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.560507</v>
       </c>
     </row>
     <row r="126">
@@ -5638,7 +5638,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -6952,7 +6956,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8086,7 +8090,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">

--- a/output/pdf_financials_xlsx/VENI.xlsx
+++ b/output/pdf_financials_xlsx/VENI.xlsx
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.414152</v>
       </c>
     </row>
     <row r="113">
@@ -4878,7 +4878,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VENI.xlsx
+++ b/output/pdf_financials_xlsx/VENI.xlsx
@@ -4954,7 +4954,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
